--- a/backend/data/financials_by_company/0893.HK.xlsx
+++ b/backend/data/financials_by_company/0893.HK.xlsx
@@ -4286,7 +4286,7 @@
         <v>-142000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>0.998</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
